--- a/Grade 7/MS Excel- Custom Sort.xlsx
+++ b/Grade 7/MS Excel- Custom Sort.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="33">
   <si>
     <t>Match No</t>
   </si>
@@ -103,15 +103,6 @@
   </si>
   <si>
     <t>Instructions:</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Sheet 2: Sort by Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Sheet 3: Sort by Team 1 (A–Z) </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Sheet 4: Team 2 (A–Z)</t>
   </si>
   <si>
     <r>
@@ -126,11 +117,23 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Sheet 1: Sort by Venue </t>
+      <t xml:space="preserve">Sheet 1: Custom Sort by Venue </t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve"> Sheet 1: Sort by Venue </t>
+    <t xml:space="preserve"> Sheet 2: Custom Sort by Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sheet 3: Custom Sort by Team 1 (A–Z) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sheet 4:Custom Sort by Team 2 (A–Z)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sheet 4:  Custom Sort by Team 2 (A–Z)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sheet 1: Custom Sort by Venue </t>
   </si>
 </sst>
 </file>
@@ -420,6 +423,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -429,9 +435,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -720,13 +723,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="15"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="18"/>
     </row>
     <row r="2" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -744,10 +747,10 @@
       <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="17"/>
+      <c r="I2" s="14"/>
     </row>
     <row r="3" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
@@ -765,10 +768,10 @@
       <c r="E3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="17"/>
+      <c r="H3" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="14"/>
     </row>
     <row r="4" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
@@ -786,10 +789,10 @@
       <c r="E4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="17"/>
+      <c r="H4" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="14"/>
     </row>
     <row r="5" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
@@ -807,10 +810,10 @@
       <c r="E5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="17"/>
+      <c r="H5" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="14"/>
     </row>
     <row r="6" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
@@ -828,10 +831,10 @@
       <c r="E6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" s="17"/>
+      <c r="H6" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="14"/>
     </row>
     <row r="7" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
@@ -849,8 +852,8 @@
       <c r="E7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
     </row>
     <row r="8" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
@@ -1309,13 +1312,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="15"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="18"/>
     </row>
     <row r="2" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1333,7 +1336,7 @@
       <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="14" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1353,8 +1356,8 @@
       <c r="E3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="17" t="s">
-        <v>31</v>
+      <c r="H3" s="14" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -1373,11 +1376,11 @@
       <c r="E4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
+      <c r="H4" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
     </row>
     <row r="5" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
@@ -1395,8 +1398,8 @@
       <c r="E5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="17" t="s">
-        <v>28</v>
+      <c r="H5" s="14" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -1415,8 +1418,8 @@
       <c r="E6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="17" t="s">
-        <v>29</v>
+      <c r="H6" s="14" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1893,13 +1896,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="15"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -1917,7 +1920,7 @@
       <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="14" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1937,8 +1940,8 @@
       <c r="E3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="17" t="s">
-        <v>31</v>
+      <c r="H3" s="14" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -1957,8 +1960,8 @@
       <c r="E4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="17" t="s">
-        <v>27</v>
+      <c r="H4" s="14" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -1977,8 +1980,8 @@
       <c r="E5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="18" t="s">
-        <v>28</v>
+      <c r="H5" s="15" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -1997,8 +2000,8 @@
       <c r="E6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="17" t="s">
-        <v>29</v>
+      <c r="H6" s="14" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2475,13 +2478,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="15"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -2499,7 +2502,7 @@
       <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="14" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2519,8 +2522,8 @@
       <c r="E3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="17" t="s">
-        <v>31</v>
+      <c r="H3" s="14" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -2539,8 +2542,8 @@
       <c r="E4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="17" t="s">
-        <v>27</v>
+      <c r="H4" s="14" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -2559,8 +2562,8 @@
       <c r="E5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="17" t="s">
-        <v>28</v>
+      <c r="H5" s="14" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
@@ -2579,8 +2582,8 @@
       <c r="E6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="18" t="s">
-        <v>29</v>
+      <c r="H6" s="15" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
